--- a/Thread Chart/OMNi Thread Charts.xlsx
+++ b/Thread Chart/OMNi Thread Charts.xlsx
@@ -1,24 +1,27 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26529"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30431"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\fs1\InformationManagement\Procedures &amp; References\Embroidery Thread Charts\Completed\OMNi\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6782F957-2086-4000-8D0D-259A09D6CFF4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{6D0D1B88-13D3-4C1E-B720-4A6247B41C66}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="22920" yWindow="-1095" windowWidth="29040" windowHeight="15840" xr2:uid="{F028543A-CA1A-4C22-838B-894A262A5CAB}"/>
+    <workbookView xWindow="19090" yWindow="-5720" windowWidth="38620" windowHeight="21100" xr2:uid="{F028543A-CA1A-4C22-838B-894A262A5CAB}"/>
   </bookViews>
   <sheets>
     <sheet name="Robison Anton SS Rayon" sheetId="3" r:id="rId1"/>
+    <sheet name="Isacord" sheetId="4" r:id="rId2"/>
+    <sheet name="Madeira Classic" sheetId="5" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Robison Anton SS Rayon'!$A$1:$I$101</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Isacord!$A$1:$I$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Robison Anton SS Rayon'!$A$1:$I$103</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191028"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -26,7 +29,12 @@
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
         <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -34,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="313" uniqueCount="125">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="394" uniqueCount="133">
   <si>
     <t>Thread Name</t>
   </si>
@@ -48,6 +56,9 @@
     <t>Thread Number</t>
   </si>
   <si>
+    <t>Monitor Display Color</t>
+  </si>
+  <si>
     <t>PMS Number</t>
   </si>
   <si>
@@ -60,355 +71,376 @@
     <t>B</t>
   </si>
   <si>
+    <t>Black</t>
+  </si>
+  <si>
+    <t>Blacks</t>
+  </si>
+  <si>
+    <t>RA SSR 9</t>
+  </si>
+  <si>
+    <t>BlackC</t>
+  </si>
+  <si>
+    <t>Ice Blue</t>
+  </si>
+  <si>
+    <t>Blues</t>
+  </si>
+  <si>
+    <t>Cristy Blue</t>
+  </si>
+  <si>
+    <t>Ultra Blue</t>
+  </si>
+  <si>
+    <t>Misty</t>
+  </si>
+  <si>
+    <t>Aquamarine</t>
+  </si>
+  <si>
+    <t>Jay Blue</t>
+  </si>
+  <si>
+    <t>Oriental Blue</t>
+  </si>
+  <si>
+    <t>Pacific Blue</t>
+  </si>
+  <si>
+    <t>Blue</t>
+  </si>
+  <si>
+    <t>Slate Blue</t>
+  </si>
+  <si>
+    <t>Imperial Blue</t>
+  </si>
+  <si>
+    <t>Blue Suede</t>
+  </si>
+  <si>
+    <t>Jamie Blue</t>
+  </si>
+  <si>
+    <t>Light Navy</t>
+  </si>
+  <si>
+    <t>Navy</t>
+  </si>
+  <si>
+    <t>Ivory</t>
+  </si>
+  <si>
+    <t>Browns</t>
+  </si>
+  <si>
+    <t>Ecru</t>
+  </si>
+  <si>
+    <t>Seashell</t>
+  </si>
+  <si>
+    <t>Platinum</t>
+  </si>
+  <si>
+    <t>Tan</t>
+  </si>
+  <si>
+    <t>Perfect Tan</t>
+  </si>
+  <si>
+    <t>Golden Tan</t>
+  </si>
+  <si>
+    <t>Ashley Gold</t>
+  </si>
+  <si>
+    <t>Copper</t>
+  </si>
+  <si>
+    <t>Hazel</t>
+  </si>
+  <si>
+    <t>Sand Dune</t>
+  </si>
+  <si>
+    <t>Chocolate</t>
+  </si>
+  <si>
+    <t>Sienna</t>
+  </si>
+  <si>
+    <t>Coffee Bean</t>
+  </si>
+  <si>
+    <t>Dark Brown</t>
+  </si>
+  <si>
+    <t>Steel Gray</t>
+  </si>
+  <si>
+    <t>Grays</t>
+  </si>
+  <si>
+    <t>Skylight</t>
+  </si>
+  <si>
+    <t>Cinder</t>
+  </si>
+  <si>
+    <t>Banner Gray</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud </t>
+  </si>
+  <si>
+    <t>Gull</t>
+  </si>
+  <si>
+    <t>Gray Rod</t>
+  </si>
+  <si>
+    <t>Silvery Gray</t>
+  </si>
+  <si>
+    <t>Twilight</t>
+  </si>
+  <si>
+    <t>Charcoal</t>
+  </si>
+  <si>
+    <t>Warm Gray 11</t>
+  </si>
+  <si>
+    <t>Metal</t>
+  </si>
+  <si>
+    <t>Black Chrome</t>
+  </si>
+  <si>
+    <t>Black 7</t>
+  </si>
+  <si>
+    <t>Mint</t>
+  </si>
+  <si>
+    <t>Greens</t>
+  </si>
+  <si>
+    <t>Pebblestone</t>
+  </si>
+  <si>
+    <t>Palm Leaf</t>
+  </si>
+  <si>
+    <t>Aqua Pearl</t>
+  </si>
+  <si>
+    <t>Erin Green</t>
+  </si>
+  <si>
+    <t>Teal</t>
+  </si>
+  <si>
+    <t>Pine Green</t>
+  </si>
+  <si>
+    <t>Kelly</t>
+  </si>
+  <si>
+    <t>Olive Drab</t>
+  </si>
+  <si>
+    <t>Evergreen</t>
+  </si>
+  <si>
+    <t>Harbor Green</t>
+  </si>
+  <si>
+    <t>Dress Green</t>
+  </si>
+  <si>
+    <t>Dark Army Green</t>
+  </si>
+  <si>
+    <t>Green Sail</t>
+  </si>
+  <si>
+    <t>Dark Teal</t>
+  </si>
+  <si>
+    <t>Pumpkin</t>
+  </si>
+  <si>
+    <t>Oranges</t>
+  </si>
+  <si>
+    <t>Golden Poppy</t>
+  </si>
+  <si>
+    <t>Dark Tex Orange</t>
+  </si>
+  <si>
+    <t>Sun Orange</t>
+  </si>
+  <si>
+    <t>Rust</t>
+  </si>
+  <si>
+    <t>Saffron</t>
+  </si>
+  <si>
+    <t>Tawny</t>
+  </si>
+  <si>
+    <t>Pinks</t>
+  </si>
+  <si>
+    <t>Pink</t>
+  </si>
+  <si>
+    <t>Bisque</t>
+  </si>
+  <si>
+    <t>Rose</t>
+  </si>
+  <si>
+    <t>Floral Pink</t>
+  </si>
+  <si>
+    <t>Bitteroot</t>
+  </si>
+  <si>
+    <t>Ruby Glint</t>
+  </si>
+  <si>
+    <t>New Berry</t>
+  </si>
+  <si>
+    <t>Tulip</t>
+  </si>
+  <si>
+    <t>Purples</t>
+  </si>
+  <si>
+    <t>Iris</t>
+  </si>
+  <si>
+    <t>Plum Wine</t>
+  </si>
+  <si>
+    <t>Mulberry</t>
+  </si>
+  <si>
+    <t>Purple</t>
+  </si>
+  <si>
+    <t>Dark Purple</t>
+  </si>
+  <si>
+    <t>Violet Blue</t>
+  </si>
+  <si>
+    <t>Radiant Red</t>
+  </si>
+  <si>
+    <t>Reds</t>
+  </si>
+  <si>
+    <t>Tuxedo Red</t>
+  </si>
+  <si>
+    <t>Foxy Red</t>
+  </si>
+  <si>
+    <t>Burgundy</t>
+  </si>
+  <si>
+    <t>Terra Cotta</t>
+  </si>
+  <si>
+    <t>Russet</t>
+  </si>
+  <si>
+    <t>Wine</t>
+  </si>
+  <si>
+    <t>Dark Maroon</t>
+  </si>
+  <si>
+    <t>Snow White</t>
+  </si>
+  <si>
+    <t>Whites</t>
+  </si>
+  <si>
+    <t>Trans. White</t>
+  </si>
+  <si>
+    <t>Maize</t>
+  </si>
+  <si>
+    <t>Yellows</t>
+  </si>
+  <si>
+    <t>Lemon</t>
+  </si>
+  <si>
+    <t>Canary Yellow</t>
+  </si>
+  <si>
+    <t>New Gold</t>
+  </si>
+  <si>
+    <t>Honey</t>
+  </si>
+  <si>
+    <t>Goldenrod</t>
+  </si>
+  <si>
+    <t>Marigold</t>
+  </si>
+  <si>
+    <t>Manila</t>
+  </si>
+  <si>
+    <t>Buttercup</t>
+  </si>
+  <si>
     <t>Yellow</t>
   </si>
   <si>
-    <t>RA SSR 9</t>
+    <t>14 Kt. Gold</t>
+  </si>
+  <si>
+    <t>Shimmering Gold</t>
   </si>
   <si>
     <t>Sun Gold</t>
   </si>
   <si>
-    <t>Marigold</t>
-  </si>
-  <si>
-    <t>Canary Yellow</t>
-  </si>
-  <si>
-    <t>Goldenrod</t>
-  </si>
-  <si>
-    <t>Honey</t>
-  </si>
-  <si>
-    <t>Maize</t>
-  </si>
-  <si>
-    <t>Lemon</t>
-  </si>
-  <si>
     <t>Ginger</t>
   </si>
   <si>
-    <t>New Gold</t>
-  </si>
-  <si>
-    <t>Manila</t>
-  </si>
-  <si>
-    <t>Shimmering Gold</t>
-  </si>
-  <si>
-    <t>Buttercup</t>
-  </si>
-  <si>
-    <t>14 Kt. Gold</t>
-  </si>
-  <si>
-    <t>Grays</t>
-  </si>
-  <si>
-    <t>Twilight</t>
-  </si>
-  <si>
-    <t>Charcoal</t>
-  </si>
-  <si>
-    <t>Warm Gray 11</t>
-  </si>
-  <si>
-    <t>Steel Gray</t>
-  </si>
-  <si>
-    <t>Cinder</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud </t>
-  </si>
-  <si>
-    <t>Silvery Gray</t>
-  </si>
-  <si>
-    <t>Black Chrome</t>
-  </si>
-  <si>
-    <t>Black 7</t>
-  </si>
-  <si>
-    <t>Gray Rod</t>
-  </si>
-  <si>
-    <t>Banner Gray</t>
-  </si>
-  <si>
-    <t>Rust</t>
-  </si>
-  <si>
-    <t>Pumpkin</t>
-  </si>
-  <si>
-    <t>Saffron</t>
-  </si>
-  <si>
-    <t>Golden Poppy</t>
-  </si>
-  <si>
-    <t>Sun Orange</t>
-  </si>
-  <si>
-    <t>Dark Tex Orange</t>
-  </si>
-  <si>
-    <t>Blue</t>
-  </si>
-  <si>
-    <t>Navy</t>
-  </si>
-  <si>
-    <t>Slate Blue</t>
-  </si>
-  <si>
-    <t>Ice Blue</t>
-  </si>
-  <si>
-    <t>Oriental Blue</t>
-  </si>
-  <si>
-    <t>Imperial Blue</t>
-  </si>
-  <si>
-    <t>Light Navy</t>
-  </si>
-  <si>
-    <t>Aquamarine</t>
-  </si>
-  <si>
-    <t>Misty</t>
-  </si>
-  <si>
-    <t>Cristy Blue</t>
-  </si>
-  <si>
-    <t>Jay Blue</t>
-  </si>
-  <si>
-    <t>Jamie Blue</t>
-  </si>
-  <si>
-    <t>Pacific Blue</t>
-  </si>
-  <si>
-    <t>Ultra Blue</t>
-  </si>
-  <si>
-    <t>Blue Suede</t>
-  </si>
-  <si>
-    <t>Wine</t>
-  </si>
-  <si>
-    <t>Burgundy</t>
-  </si>
-  <si>
-    <t>Russet</t>
-  </si>
-  <si>
-    <t>Foxy Red</t>
-  </si>
-  <si>
-    <t>Radiant Red</t>
-  </si>
-  <si>
-    <t>Terra Cotta</t>
-  </si>
-  <si>
-    <t>Dark Maroon</t>
-  </si>
-  <si>
-    <t>Tuxedo Red</t>
-  </si>
-  <si>
-    <t>Purple</t>
-  </si>
-  <si>
-    <t>Tulip</t>
-  </si>
-  <si>
-    <t>Iris</t>
-  </si>
-  <si>
-    <t>Mulberry</t>
-  </si>
-  <si>
-    <t>Dark Purple</t>
-  </si>
-  <si>
-    <t>Violet Blue</t>
-  </si>
-  <si>
-    <t>Plum Wine</t>
-  </si>
-  <si>
-    <t>Greens</t>
-  </si>
-  <si>
-    <t>Purples</t>
-  </si>
-  <si>
-    <t>Reds</t>
-  </si>
-  <si>
-    <t>Blues</t>
-  </si>
-  <si>
-    <t>Oranges</t>
-  </si>
-  <si>
-    <t>Yellows</t>
-  </si>
-  <si>
-    <t>Mint</t>
-  </si>
-  <si>
-    <t>Kelly</t>
-  </si>
-  <si>
-    <t>Palm Leaf</t>
-  </si>
-  <si>
-    <t>Teal</t>
-  </si>
-  <si>
-    <t>Evergreen</t>
-  </si>
-  <si>
-    <t>Olive Drab</t>
-  </si>
-  <si>
-    <t>Erin Green</t>
-  </si>
-  <si>
-    <t>Pine Green</t>
-  </si>
-  <si>
-    <t>Harbor Green</t>
-  </si>
-  <si>
-    <t>Dark Teal</t>
-  </si>
-  <si>
-    <t>Green Sail</t>
-  </si>
-  <si>
-    <t>Aqua Pearl</t>
-  </si>
-  <si>
-    <t>Pebblestone</t>
-  </si>
-  <si>
-    <t>Dark Army Green</t>
-  </si>
-  <si>
-    <t>Dress Green</t>
-  </si>
-  <si>
-    <t>Browns</t>
-  </si>
-  <si>
-    <t>Chocolate</t>
-  </si>
-  <si>
-    <t>Ecru</t>
-  </si>
-  <si>
-    <t>Tan</t>
-  </si>
-  <si>
-    <t>Copper</t>
-  </si>
-  <si>
-    <t>Ivory</t>
-  </si>
-  <si>
-    <t>Coffee Bean</t>
-  </si>
-  <si>
-    <t>Dark Brown</t>
-  </si>
-  <si>
-    <t>Ashley Gold</t>
-  </si>
-  <si>
-    <t>Sienna</t>
-  </si>
-  <si>
-    <t>Seashell</t>
-  </si>
-  <si>
-    <t>Sand Dune</t>
-  </si>
-  <si>
-    <t>Hazel</t>
-  </si>
-  <si>
-    <t>Perfect Tan</t>
-  </si>
-  <si>
-    <t>Golden Tan</t>
-  </si>
-  <si>
-    <t>Platinum</t>
-  </si>
-  <si>
-    <t>Pink</t>
-  </si>
-  <si>
-    <t>Pinks</t>
-  </si>
-  <si>
-    <t>Tawny</t>
-  </si>
-  <si>
-    <t>Ruby Glint</t>
-  </si>
-  <si>
-    <t>Rose</t>
-  </si>
-  <si>
-    <t>Bisque</t>
-  </si>
-  <si>
-    <t>Floral Pink</t>
-  </si>
-  <si>
-    <t>New Berry</t>
-  </si>
-  <si>
-    <t>Monitor Display Color</t>
-  </si>
-  <si>
-    <t>Black</t>
-  </si>
-  <si>
-    <t>Blacks</t>
-  </si>
-  <si>
-    <t>BlackC</t>
-  </si>
-  <si>
-    <t>Snow White</t>
-  </si>
-  <si>
-    <t>Whites</t>
-  </si>
-  <si>
-    <t>Trans. White</t>
-  </si>
-  <si>
-    <t>Bitteroot</t>
-  </si>
-  <si>
-    <t>Dover Gray</t>
+    <t>NA</t>
+  </si>
+  <si>
+    <t>Isacord 40</t>
+  </si>
+  <si>
+    <t>Cool Gray 5</t>
+  </si>
+  <si>
+    <t>Cool Gray 8</t>
+  </si>
+  <si>
+    <t>Orange 021</t>
+  </si>
+  <si>
+    <t>Madeira Classic</t>
   </si>
 </sst>
 </file>
@@ -418,7 +450,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0000"/>
   </numFmts>
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -462,7 +494,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="101">
+  <fills count="117">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1059,7 +1091,103 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFBBACD6"/>
+        <fgColor rgb="FF4F5757"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF908E88"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC7C4D1"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF8AB1C4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB8B19C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF728371"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB2B2B2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF898A8C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF7F7E73"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD0DE00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC4A10E"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF4800"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF19AAD"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6F265A"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE71615"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF852740"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00ADD7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1076,7 +1204,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="103">
+  <cellXfs count="122">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1375,13 +1503,70 @@
     <xf numFmtId="0" fontId="0" fillId="99" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="164" fontId="5" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="100" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="101" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="102" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="103" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="104" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="105" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="106" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="107" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="108" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="109" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="110" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="111" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="112" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="113" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="114" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="115" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="116" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1712,23 +1897,23 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FF431DED-CC07-445B-98CD-FA1799BBCA91}">
-  <dimension ref="A1:I101"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:O103"/>
+  <sheetFormatPr defaultColWidth="0" defaultRowHeight="15" zeroHeight="1"/>
   <cols>
     <col min="1" max="1" width="20.7109375" style="1" customWidth="1"/>
     <col min="2" max="2" width="17.7109375" style="1" customWidth="1"/>
     <col min="3" max="3" width="17.5703125" style="1" customWidth="1"/>
-    <col min="4" max="4" width="19.7109375" style="101" customWidth="1"/>
+    <col min="4" max="4" width="19.7109375" style="121" customWidth="1"/>
     <col min="5" max="5" width="50.7109375" style="1" customWidth="1"/>
     <col min="6" max="6" width="17.7109375" style="1" customWidth="1"/>
-    <col min="7" max="9" width="8.85546875" style="1"/>
-    <col min="10" max="10" width="20.7109375" style="1" customWidth="1"/>
-    <col min="11" max="14" width="8.85546875" style="1"/>
-    <col min="15" max="15" width="50.7109375" style="1" customWidth="1"/>
-    <col min="16" max="16384" width="8.85546875" style="1"/>
+    <col min="7" max="9" width="8.85546875" style="1" customWidth="1"/>
+    <col min="10" max="10" width="20.7109375" style="1" hidden="1" customWidth="1"/>
+    <col min="11" max="14" width="8.85546875" style="1" hidden="1" customWidth="1"/>
+    <col min="15" max="15" width="50.7109375" style="1" hidden="1" customWidth="1"/>
+    <col min="16" max="16384" width="8.85546875" style="1" hidden="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" s="5" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" s="5" customFormat="1" ht="50.1" customHeight="1">
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
@@ -1738,41 +1923,41 @@
       <c r="C1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="102" t="s">
+      <c r="D1" s="100" t="s">
         <v>3</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>116</v>
+        <v>4</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G1" s="5" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H1" s="5" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I1" s="5" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" ht="50.1" customHeight="1">
       <c r="A2" s="1" t="s">
-        <v>117</v>
+        <v>9</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>118</v>
+        <v>10</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="D2" s="101">
+        <v>11</v>
+      </c>
+      <c r="D2" s="120">
         <v>2296</v>
       </c>
       <c r="E2" s="98"/>
       <c r="F2" s="1" t="s">
-        <v>119</v>
+        <v>12</v>
       </c>
       <c r="G2" s="1">
         <v>0</v>
@@ -1784,17 +1969,17 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:9" ht="50.1" customHeight="1">
       <c r="A3" s="1" t="s">
-        <v>44</v>
+        <v>13</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>74</v>
+        <v>14</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="D3" s="101">
+        <v>11</v>
+      </c>
+      <c r="D3" s="120">
         <v>2300</v>
       </c>
       <c r="E3" s="35"/>
@@ -1811,17 +1996,17 @@
         <v>236</v>
       </c>
     </row>
-    <row r="4" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:9" ht="50.1" customHeight="1">
       <c r="A4" s="1" t="s">
-        <v>50</v>
+        <v>15</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>74</v>
+        <v>14</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="D4" s="101">
+        <v>11</v>
+      </c>
+      <c r="D4" s="120">
         <v>2383</v>
       </c>
       <c r="E4" s="41"/>
@@ -1838,17 +2023,17 @@
         <v>237</v>
       </c>
     </row>
-    <row r="5" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:9" ht="50.1" customHeight="1">
       <c r="A5" s="1" t="s">
-        <v>54</v>
+        <v>16</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>74</v>
+        <v>14</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="D5" s="101">
+        <v>11</v>
+      </c>
+      <c r="D5" s="120">
         <v>2433</v>
       </c>
       <c r="E5" s="45"/>
@@ -1865,17 +2050,17 @@
         <v>231</v>
       </c>
     </row>
-    <row r="6" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:9" ht="50.1" customHeight="1">
       <c r="A6" s="1" t="s">
-        <v>49</v>
+        <v>17</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>74</v>
+        <v>14</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="D6" s="101">
+        <v>11</v>
+      </c>
+      <c r="D6" s="120">
         <v>2308</v>
       </c>
       <c r="E6" s="40"/>
@@ -1892,17 +2077,17 @@
         <v>200</v>
       </c>
     </row>
-    <row r="7" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:9" ht="50.1" customHeight="1">
       <c r="A7" s="1" t="s">
-        <v>48</v>
+        <v>18</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>74</v>
+        <v>14</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="D7" s="101">
+        <v>11</v>
+      </c>
+      <c r="D7" s="120">
         <v>2307</v>
       </c>
       <c r="E7" s="39"/>
@@ -1919,17 +2104,17 @@
         <v>205</v>
       </c>
     </row>
-    <row r="8" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:9" ht="50.1" customHeight="1">
       <c r="A8" s="1" t="s">
-        <v>51</v>
+        <v>19</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>74</v>
+        <v>14</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="D8" s="101">
+        <v>11</v>
+      </c>
+      <c r="D8" s="120">
         <v>2384</v>
       </c>
       <c r="E8" s="42"/>
@@ -1946,17 +2131,17 @@
         <v>216</v>
       </c>
     </row>
-    <row r="9" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:9" ht="50.1" customHeight="1">
       <c r="A9" s="1" t="s">
-        <v>45</v>
+        <v>20</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>74</v>
+        <v>14</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="D9" s="101">
+        <v>11</v>
+      </c>
+      <c r="D9" s="120">
         <v>2301</v>
       </c>
       <c r="E9" s="36"/>
@@ -1973,17 +2158,17 @@
         <v>202</v>
       </c>
     </row>
-    <row r="10" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:9" ht="50.1" customHeight="1">
       <c r="A10" s="1" t="s">
-        <v>53</v>
+        <v>21</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>74</v>
+        <v>14</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="D10" s="101">
+        <v>11</v>
+      </c>
+      <c r="D10" s="120">
         <v>2388</v>
       </c>
       <c r="E10" s="44"/>
@@ -2000,17 +2185,17 @@
         <v>185</v>
       </c>
     </row>
-    <row r="11" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:9" ht="50.1" customHeight="1">
       <c r="A11" s="1" t="s">
-        <v>41</v>
+        <v>22</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>74</v>
+        <v>14</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="D11" s="101">
+        <v>11</v>
+      </c>
+      <c r="D11" s="120">
         <v>2220</v>
       </c>
       <c r="E11" s="33"/>
@@ -2027,17 +2212,17 @@
         <v>185</v>
       </c>
     </row>
-    <row r="12" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:9" ht="50.1" customHeight="1">
       <c r="A12" s="1" t="s">
-        <v>43</v>
+        <v>23</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>74</v>
+        <v>14</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="D12" s="101">
+        <v>11</v>
+      </c>
+      <c r="D12" s="120">
         <v>2275</v>
       </c>
       <c r="E12" s="34"/>
@@ -2054,17 +2239,17 @@
         <v>147</v>
       </c>
     </row>
-    <row r="13" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:9" ht="50.1" customHeight="1">
       <c r="A13" s="1" t="s">
-        <v>46</v>
+        <v>24</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>74</v>
+        <v>14</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="D13" s="101">
+        <v>11</v>
+      </c>
+      <c r="D13" s="120">
         <v>2302</v>
       </c>
       <c r="E13" s="37"/>
@@ -2081,17 +2266,17 @@
         <v>143</v>
       </c>
     </row>
-    <row r="14" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:9" ht="50.1" customHeight="1">
       <c r="A14" s="1" t="s">
-        <v>55</v>
+        <v>25</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>74</v>
+        <v>14</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="D14" s="101">
+        <v>11</v>
+      </c>
+      <c r="D14" s="120">
         <v>2438</v>
       </c>
       <c r="E14" s="46"/>
@@ -2108,17 +2293,17 @@
         <v>159</v>
       </c>
     </row>
-    <row r="15" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:9" ht="50.1" customHeight="1">
       <c r="A15" s="1" t="s">
-        <v>52</v>
+        <v>26</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>74</v>
+        <v>14</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="D15" s="101">
+        <v>11</v>
+      </c>
+      <c r="D15" s="120">
         <v>2385</v>
       </c>
       <c r="E15" s="43"/>
@@ -2135,17 +2320,17 @@
         <v>147</v>
       </c>
     </row>
-    <row r="16" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:9" ht="50.1" customHeight="1">
       <c r="A16" s="1" t="s">
-        <v>47</v>
+        <v>27</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>74</v>
+        <v>14</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="D16" s="101">
+        <v>11</v>
+      </c>
+      <c r="D16" s="120">
         <v>2303</v>
       </c>
       <c r="E16" s="38"/>
@@ -2162,17 +2347,17 @@
         <v>90</v>
       </c>
     </row>
-    <row r="17" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:9" ht="50.1" customHeight="1">
       <c r="A17" s="1" t="s">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>74</v>
+        <v>14</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="D17" s="101">
+        <v>11</v>
+      </c>
+      <c r="D17" s="120">
         <v>2215</v>
       </c>
       <c r="E17" s="32"/>
@@ -2189,17 +2374,17 @@
         <v>43</v>
       </c>
     </row>
-    <row r="18" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:9" ht="50.1" customHeight="1">
       <c r="A18" s="1" t="s">
-        <v>97</v>
+        <v>29</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>92</v>
+        <v>30</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="D18" s="101">
+        <v>11</v>
+      </c>
+      <c r="D18" s="120">
         <v>2335</v>
       </c>
       <c r="E18" s="82"/>
@@ -2216,17 +2401,17 @@
         <v>176</v>
       </c>
     </row>
-    <row r="19" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:9" ht="50.1" customHeight="1">
       <c r="A19" s="1" t="s">
-        <v>94</v>
+        <v>31</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>92</v>
+        <v>30</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="D19" s="101">
+        <v>11</v>
+      </c>
+      <c r="D19" s="120">
         <v>2232</v>
       </c>
       <c r="E19" s="78"/>
@@ -2243,17 +2428,17 @@
         <v>179</v>
       </c>
     </row>
-    <row r="20" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:9" ht="50.1" customHeight="1">
       <c r="A20" s="1" t="s">
-        <v>102</v>
+        <v>32</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>92</v>
+        <v>30</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="D20" s="101">
+        <v>11</v>
+      </c>
+      <c r="D20" s="120">
         <v>2476</v>
       </c>
       <c r="E20" s="86"/>
@@ -2270,17 +2455,17 @@
         <v>133</v>
       </c>
     </row>
-    <row r="21" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:9" ht="50.1" customHeight="1">
       <c r="A21" s="1" t="s">
-        <v>107</v>
+        <v>33</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>92</v>
+        <v>30</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="D21" s="101">
+        <v>11</v>
+      </c>
+      <c r="D21" s="120">
         <v>2571</v>
       </c>
       <c r="E21" s="90"/>
@@ -2297,17 +2482,17 @@
         <v>153</v>
       </c>
     </row>
-    <row r="22" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:9" ht="50.1" customHeight="1">
       <c r="A22" s="1" t="s">
-        <v>95</v>
+        <v>34</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>92</v>
+        <v>30</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="D22" s="101">
+        <v>11</v>
+      </c>
+      <c r="D22" s="120">
         <v>2273</v>
       </c>
       <c r="E22" s="79"/>
@@ -2324,17 +2509,17 @@
         <v>115</v>
       </c>
     </row>
-    <row r="23" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:9" ht="50.1" customHeight="1">
       <c r="A23" s="1" t="s">
-        <v>105</v>
+        <v>35</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>92</v>
+        <v>30</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="D23" s="101">
+        <v>11</v>
+      </c>
+      <c r="D23" s="120">
         <v>2568</v>
       </c>
       <c r="E23" s="81"/>
@@ -2351,17 +2536,17 @@
         <v>126</v>
       </c>
     </row>
-    <row r="24" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:9" ht="50.1" customHeight="1">
       <c r="A24" s="1" t="s">
-        <v>106</v>
+        <v>36</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>92</v>
+        <v>30</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="D24" s="101">
+        <v>11</v>
+      </c>
+      <c r="D24" s="120">
         <v>2570</v>
       </c>
       <c r="E24" s="89"/>
@@ -2378,17 +2563,17 @@
         <v>117</v>
       </c>
     </row>
-    <row r="25" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:9" ht="50.1" customHeight="1">
       <c r="A25" s="1" t="s">
-        <v>100</v>
+        <v>37</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>92</v>
+        <v>30</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="D25" s="101">
+        <v>11</v>
+      </c>
+      <c r="D25" s="120">
         <v>2401</v>
       </c>
       <c r="E25" s="85"/>
@@ -2405,17 +2590,17 @@
         <v>106</v>
       </c>
     </row>
-    <row r="26" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:9" ht="50.1" customHeight="1">
       <c r="A26" s="1" t="s">
-        <v>96</v>
+        <v>38</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>92</v>
+        <v>30</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="D26" s="101">
+        <v>11</v>
+      </c>
+      <c r="D26" s="120">
         <v>2295</v>
       </c>
       <c r="E26" s="80"/>
@@ -2432,17 +2617,17 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:9" ht="50.1" customHeight="1">
       <c r="A27" s="1" t="s">
-        <v>104</v>
+        <v>39</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>92</v>
+        <v>30</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="D27" s="101">
+        <v>11</v>
+      </c>
+      <c r="D27" s="120">
         <v>2481</v>
       </c>
       <c r="E27" s="88"/>
@@ -2459,17 +2644,17 @@
         <v>37</v>
       </c>
     </row>
-    <row r="28" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:9" ht="50.1" customHeight="1">
       <c r="A28" s="1" t="s">
-        <v>103</v>
+        <v>40</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>92</v>
+        <v>30</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="D28" s="101">
+        <v>11</v>
+      </c>
+      <c r="D28" s="120">
         <v>2477</v>
       </c>
       <c r="E28" s="87"/>
@@ -2486,17 +2671,17 @@
         <v>61</v>
       </c>
     </row>
-    <row r="29" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:9" ht="50.1" customHeight="1">
       <c r="A29" s="1" t="s">
-        <v>93</v>
+        <v>41</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>92</v>
+        <v>30</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="D29" s="101">
+        <v>11</v>
+      </c>
+      <c r="D29" s="120">
         <v>2227</v>
       </c>
       <c r="E29" s="77"/>
@@ -2513,17 +2698,17 @@
         <v>11</v>
       </c>
     </row>
-    <row r="30" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:9" ht="50.1" customHeight="1">
       <c r="A30" s="1" t="s">
-        <v>101</v>
+        <v>42</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>92</v>
+        <v>30</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="D30" s="101">
+        <v>11</v>
+      </c>
+      <c r="D30" s="120">
         <v>2402</v>
       </c>
       <c r="E30" s="77"/>
@@ -2540,17 +2725,17 @@
         <v>11</v>
       </c>
     </row>
-    <row r="31" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:9" ht="50.1" customHeight="1">
       <c r="A31" s="1" t="s">
-        <v>98</v>
+        <v>43</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>92</v>
+        <v>30</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="D31" s="101">
+        <v>11</v>
+      </c>
+      <c r="D31" s="120">
         <v>2339</v>
       </c>
       <c r="E31" s="83"/>
@@ -2567,17 +2752,17 @@
         <v>50</v>
       </c>
     </row>
-    <row r="32" spans="1:9" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:9" ht="41.25" customHeight="1">
       <c r="A32" s="1" t="s">
-        <v>99</v>
+        <v>44</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>92</v>
+        <v>30</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="D32" s="101">
+        <v>11</v>
+      </c>
+      <c r="D32" s="120">
         <v>2372</v>
       </c>
       <c r="E32" s="84"/>
@@ -2594,17 +2779,17 @@
         <v>28</v>
       </c>
     </row>
-    <row r="33" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:9" ht="50.1" customHeight="1">
       <c r="A33" s="1" t="s">
-        <v>27</v>
+        <v>45</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="D33" s="101">
+        <v>11</v>
+      </c>
+      <c r="D33" s="120">
         <v>2274</v>
       </c>
       <c r="E33" s="19"/>
@@ -2621,44 +2806,44 @@
         <v>224</v>
       </c>
     </row>
-    <row r="34" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:9" ht="50.1" customHeight="1">
       <c r="A34" s="1" t="s">
-        <v>124</v>
+        <v>47</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="D34" s="101">
-        <v>2405</v>
-      </c>
-      <c r="E34" s="100"/>
+        <v>11</v>
+      </c>
+      <c r="D34" s="120">
+        <v>2482</v>
+      </c>
+      <c r="E34" s="103"/>
       <c r="F34" s="1">
-        <v>2092</v>
+        <v>5305</v>
       </c>
       <c r="G34" s="1">
-        <v>187</v>
+        <v>199</v>
       </c>
       <c r="H34" s="1">
-        <v>172</v>
+        <v>196</v>
       </c>
       <c r="I34" s="1">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="35" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9" ht="50.1" customHeight="1">
       <c r="A35" s="1" t="s">
-        <v>28</v>
+        <v>48</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="D35" s="101">
+        <v>11</v>
+      </c>
+      <c r="D35" s="120">
         <v>2404</v>
       </c>
       <c r="E35" s="20"/>
@@ -2675,17 +2860,17 @@
         <v>195</v>
       </c>
     </row>
-    <row r="36" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:9" ht="50.1" customHeight="1">
       <c r="A36" s="1" t="s">
-        <v>34</v>
+        <v>49</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="D36" s="101">
+        <v>11</v>
+      </c>
+      <c r="D36" s="121">
         <v>2585</v>
       </c>
       <c r="E36" s="25"/>
@@ -2702,17 +2887,17 @@
         <v>172</v>
       </c>
     </row>
-    <row r="37" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:9" ht="50.1" customHeight="1">
       <c r="A37" s="1" t="s">
-        <v>29</v>
+        <v>50</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="D37" s="101">
+        <v>11</v>
+      </c>
+      <c r="D37" s="121">
         <v>2483</v>
       </c>
       <c r="E37" s="21"/>
@@ -2729,1741 +2914,2609 @@
         <v>161</v>
       </c>
     </row>
-    <row r="38" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:9" ht="50.1" customHeight="1">
       <c r="A38" s="1" t="s">
-        <v>33</v>
+        <v>51</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="D38" s="101">
+        <v>11</v>
+      </c>
+      <c r="D38" s="104">
+        <v>2731</v>
+      </c>
+      <c r="E38" s="102"/>
+      <c r="F38" s="1">
+        <v>7539</v>
+      </c>
+      <c r="G38" s="1">
+        <v>144</v>
+      </c>
+      <c r="H38" s="1">
+        <v>142</v>
+      </c>
+      <c r="I38" s="1">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9" ht="50.1" customHeight="1">
+      <c r="A39" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D39" s="121">
         <v>2572</v>
       </c>
-      <c r="E38" s="24"/>
-      <c r="F38" s="1">
+      <c r="E39" s="24"/>
+      <c r="F39" s="1">
         <v>7530</v>
       </c>
-      <c r="G38" s="1">
+      <c r="G39" s="1">
         <v>164</v>
       </c>
-      <c r="H38" s="1">
+      <c r="H39" s="1">
         <v>147</v>
       </c>
-      <c r="I38" s="1">
+      <c r="I39" s="1">
         <v>130</v>
       </c>
     </row>
-    <row r="39" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="B39" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="C39" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="D39" s="101">
+    <row r="40" spans="1:9" ht="50.1" hidden="1" customHeight="1">
+      <c r="A40" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="C40" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D40" s="121">
         <v>2484</v>
       </c>
-      <c r="E39" s="22"/>
-      <c r="F39" s="1">
+      <c r="E40" s="22"/>
+      <c r="F40" s="1">
         <v>2360</v>
       </c>
-      <c r="G39" s="1">
+      <c r="G40" s="1">
         <v>124</v>
       </c>
-      <c r="H39" s="1">
+      <c r="H40" s="1">
         <v>119</v>
       </c>
-      <c r="I39" s="1">
+      <c r="I40" s="1">
         <v>139</v>
       </c>
     </row>
-    <row r="40" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="B40" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="C40" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="D40" s="101">
+    <row r="41" spans="1:9" ht="50.1" customHeight="1">
+      <c r="A41" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="C41" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D41" s="121">
         <v>2217</v>
       </c>
-      <c r="E40" s="17"/>
-      <c r="F40" s="1">
+      <c r="E41" s="17"/>
+      <c r="F41" s="1">
         <v>2364</v>
       </c>
-      <c r="G40" s="1">
+      <c r="G41" s="1">
         <v>103</v>
       </c>
-      <c r="H40" s="1">
+      <c r="H41" s="1">
         <v>87</v>
       </c>
-      <c r="I40" s="1">
+      <c r="I41" s="1">
         <v>106</v>
       </c>
     </row>
-    <row r="41" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="B41" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="C41" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="D41" s="101">
+    <row r="42" spans="1:9" ht="50.1" customHeight="1">
+      <c r="A42" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="C42" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D42" s="121">
         <v>2265</v>
       </c>
-      <c r="E41" s="18"/>
-      <c r="F41" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="G41" s="1">
+      <c r="E42" s="18"/>
+      <c r="F42" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="G42" s="1">
         <v>111</v>
       </c>
-      <c r="H41" s="1">
+      <c r="H42" s="1">
         <v>97</v>
       </c>
-      <c r="I41" s="1">
+      <c r="I42" s="1">
         <v>88</v>
       </c>
     </row>
-    <row r="42" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="B42" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="C42" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="D42" s="101">
+    <row r="43" spans="1:9" ht="50.1" customHeight="1">
+      <c r="A43" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="C43" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D43" s="104">
+        <v>2407</v>
+      </c>
+      <c r="E43" s="101"/>
+      <c r="F43" s="1">
+        <v>445</v>
+      </c>
+      <c r="G43" s="1">
+        <v>79</v>
+      </c>
+      <c r="H43" s="1">
+        <v>87</v>
+      </c>
+      <c r="I43" s="1">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9" ht="50.1" customHeight="1">
+      <c r="A44" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="C44" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D44" s="121">
         <v>2541</v>
       </c>
-      <c r="E42" s="23"/>
-      <c r="F42" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="G42" s="1">
+      <c r="E44" s="23"/>
+      <c r="F44" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="G44" s="1">
         <v>60</v>
       </c>
-      <c r="H42" s="1">
+      <c r="H44" s="1">
         <v>56</v>
       </c>
-      <c r="I42" s="1">
+      <c r="I44" s="1">
         <v>52</v>
       </c>
     </row>
-    <row r="43" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="B43" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="C43" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="D43" s="101">
+    <row r="45" spans="1:9" ht="50.1" customHeight="1">
+      <c r="A45" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="C45" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D45" s="121">
         <v>2238</v>
       </c>
-      <c r="E43" s="62"/>
-      <c r="F43" s="1">
+      <c r="E45" s="62"/>
+      <c r="F45" s="1">
         <v>2254</v>
       </c>
-      <c r="G43" s="1">
+      <c r="G45" s="1">
         <v>174</v>
       </c>
-      <c r="H43" s="1">
+      <c r="H45" s="1">
         <v>222</v>
       </c>
-      <c r="I43" s="1">
+      <c r="I45" s="1">
         <v>179</v>
       </c>
     </row>
-    <row r="44" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="B44" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="C44" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="D44" s="101">
+    <row r="46" spans="1:9" ht="50.1" customHeight="1">
+      <c r="A46" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="C46" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D46" s="121">
         <v>2547</v>
       </c>
-      <c r="E44" s="74"/>
-      <c r="F44" s="1">
+      <c r="E46" s="74"/>
+      <c r="F46" s="1">
         <v>2295</v>
       </c>
-      <c r="G44" s="1">
+      <c r="G46" s="1">
         <v>226</v>
       </c>
-      <c r="H44" s="1">
+      <c r="H46" s="1">
         <v>234</v>
       </c>
-      <c r="I44" s="1">
+      <c r="I46" s="1">
         <v>134</v>
       </c>
     </row>
-    <row r="45" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="B45" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="C45" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="D45" s="101">
+    <row r="47" spans="1:9" ht="50.1" customHeight="1">
+      <c r="A47" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="B47" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="C47" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D47" s="121">
         <v>2241</v>
       </c>
-      <c r="E45" s="64"/>
-      <c r="F45" s="1">
+      <c r="E47" s="64"/>
+      <c r="F47" s="1">
         <v>5655</v>
       </c>
-      <c r="G45" s="1">
+      <c r="G47" s="1">
         <v>179</v>
-      </c>
-      <c r="H45" s="1">
-        <v>188</v>
-      </c>
-      <c r="I45" s="1">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="46" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="B46" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="C46" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="D46" s="101">
-        <v>2516</v>
-      </c>
-      <c r="E46" s="73"/>
-      <c r="F46" s="1">
-        <v>3255</v>
-      </c>
-      <c r="G46" s="1">
-        <v>29</v>
-      </c>
-      <c r="H46" s="1">
-        <v>211</v>
-      </c>
-      <c r="I46" s="1">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="47" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="B47" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="C47" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="D47" s="101">
-        <v>2320</v>
-      </c>
-      <c r="E47" s="68"/>
-      <c r="F47" s="1">
-        <v>376</v>
-      </c>
-      <c r="G47" s="1">
-        <v>131</v>
       </c>
       <c r="H47" s="1">
         <v>188</v>
       </c>
       <c r="I47" s="1">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="48" spans="1:9" ht="50.1" customHeight="1">
+      <c r="A48" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="B48" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="C48" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D48" s="121">
+        <v>2516</v>
+      </c>
+      <c r="E48" s="73"/>
+      <c r="F48" s="1">
+        <v>3255</v>
+      </c>
+      <c r="G48" s="1">
+        <v>29</v>
+      </c>
+      <c r="H48" s="1">
+        <v>211</v>
+      </c>
+      <c r="I48" s="1">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="49" spans="1:9" ht="50.1" customHeight="1">
+      <c r="A49" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="B49" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="C49" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D49" s="121">
+        <v>2320</v>
+      </c>
+      <c r="E49" s="68"/>
+      <c r="F49" s="1">
+        <v>376</v>
+      </c>
+      <c r="G49" s="1">
+        <v>131</v>
+      </c>
+      <c r="H49" s="1">
+        <v>188</v>
+      </c>
+      <c r="I49" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="B48" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="C48" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="D48" s="101">
+    <row r="50" spans="1:9" ht="50.1" customHeight="1">
+      <c r="A50" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="B50" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="C50" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D50" s="121">
         <v>2309</v>
       </c>
-      <c r="E48" s="65"/>
-      <c r="F48" s="1">
+      <c r="E50" s="65"/>
+      <c r="F50" s="1">
         <v>633</v>
-      </c>
-      <c r="G48" s="1">
-        <v>0</v>
-      </c>
-      <c r="H48" s="1">
-        <v>113</v>
-      </c>
-      <c r="I48" s="1">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="49" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="B49" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="C49" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="D49" s="101">
-        <v>2391</v>
-      </c>
-      <c r="E49" s="69"/>
-      <c r="F49" s="1">
-        <v>328</v>
-      </c>
-      <c r="G49" s="1">
-        <v>0</v>
-      </c>
-      <c r="H49" s="1">
-        <v>112</v>
-      </c>
-      <c r="I49" s="1">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="50" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="B50" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="C50" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="D50" s="101">
-        <v>2240</v>
-      </c>
-      <c r="E50" s="63"/>
-      <c r="F50" s="1">
-        <v>356</v>
       </c>
       <c r="G50" s="1">
         <v>0</v>
       </c>
       <c r="H50" s="1">
-        <v>120</v>
+        <v>113</v>
       </c>
       <c r="I50" s="1">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="51" spans="1:9" ht="49.5" customHeight="1" x14ac:dyDescent="0.25">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="51" spans="1:9" ht="50.1" customHeight="1">
       <c r="A51" s="1" t="s">
-        <v>82</v>
+        <v>67</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="D51" s="101">
-        <v>2317</v>
-      </c>
-      <c r="E51" s="67"/>
+        <v>11</v>
+      </c>
+      <c r="D51" s="121">
+        <v>2391</v>
+      </c>
+      <c r="E51" s="69"/>
       <c r="F51" s="1">
-        <v>2308</v>
+        <v>328</v>
       </c>
       <c r="G51" s="1">
-        <v>91</v>
+        <v>0</v>
       </c>
       <c r="H51" s="1">
-        <v>85</v>
+        <v>112</v>
       </c>
       <c r="I51" s="1">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="52" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="52" spans="1:9" ht="50.1" customHeight="1">
       <c r="A52" s="1" t="s">
-        <v>81</v>
+        <v>68</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="D52" s="101">
-        <v>2315</v>
-      </c>
-      <c r="E52" s="66"/>
+        <v>11</v>
+      </c>
+      <c r="D52" s="121">
+        <v>2240</v>
+      </c>
+      <c r="E52" s="63"/>
       <c r="F52" s="1">
-        <v>3425</v>
+        <v>356</v>
       </c>
       <c r="G52" s="1">
         <v>0</v>
       </c>
       <c r="H52" s="1">
+        <v>120</v>
+      </c>
+      <c r="I52" s="1">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="53" spans="1:9" ht="49.5" customHeight="1">
+      <c r="A53" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="B53" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="C53" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D53" s="121">
+        <v>2317</v>
+      </c>
+      <c r="E53" s="67"/>
+      <c r="F53" s="1">
+        <v>2308</v>
+      </c>
+      <c r="G53" s="1">
+        <v>91</v>
+      </c>
+      <c r="H53" s="1">
+        <v>85</v>
+      </c>
+      <c r="I53" s="1">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="54" spans="1:9" ht="50.1" customHeight="1">
+      <c r="A54" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="B54" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="C54" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D54" s="121">
+        <v>2315</v>
+      </c>
+      <c r="E54" s="66"/>
+      <c r="F54" s="1">
+        <v>3425</v>
+      </c>
+      <c r="G54" s="1">
+        <v>0</v>
+      </c>
+      <c r="H54" s="1">
         <v>97</v>
       </c>
-      <c r="I52" s="1">
+      <c r="I54" s="1">
         <v>64</v>
       </c>
     </row>
-    <row r="53" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A53" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="B53" s="1" t="s">
+    <row r="55" spans="1:9" ht="50.1" customHeight="1">
+      <c r="A55" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="C53" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="D53" s="101">
+      <c r="B55" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="C55" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D55" s="121">
         <v>2392</v>
       </c>
-      <c r="E53" s="70"/>
-      <c r="F53" s="1">
+      <c r="E55" s="70"/>
+      <c r="F55" s="1">
         <v>561</v>
       </c>
-      <c r="G53" s="1">
+      <c r="G55" s="1">
         <v>7</v>
       </c>
-      <c r="H53" s="1">
+      <c r="H55" s="1">
         <v>88</v>
       </c>
-      <c r="I53" s="1">
+      <c r="I55" s="1">
         <v>76</v>
       </c>
     </row>
-    <row r="54" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A54" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="B54" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="C54" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="D54" s="101">
+    <row r="56" spans="1:9" ht="50.1" customHeight="1">
+      <c r="A56" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="B56" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="C56" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D56" s="121">
         <v>2584</v>
       </c>
-      <c r="E54" s="76"/>
-      <c r="F54" s="1">
+      <c r="E56" s="76"/>
+      <c r="F56" s="1">
         <v>2410</v>
       </c>
-      <c r="G54" s="1">
+      <c r="G56" s="1">
         <v>67</v>
       </c>
-      <c r="H54" s="1">
+      <c r="H56" s="1">
         <v>89</v>
       </c>
-      <c r="I54" s="1">
+      <c r="I56" s="1">
         <v>60</v>
       </c>
     </row>
-    <row r="55" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="B55" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="C55" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="D55" s="101">
+    <row r="57" spans="1:9" ht="50.1" customHeight="1">
+      <c r="A57" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="B57" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="C57" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D57" s="121">
         <v>2553</v>
       </c>
-      <c r="E55" s="75"/>
-      <c r="F55" s="1">
+      <c r="E57" s="75"/>
+      <c r="F57" s="1">
         <v>7736</v>
       </c>
-      <c r="G55" s="1">
+      <c r="G57" s="1">
         <v>56</v>
       </c>
-      <c r="H55" s="1">
+      <c r="H57" s="1">
         <v>84</v>
       </c>
-      <c r="I55" s="1">
+      <c r="I57" s="1">
         <v>65</v>
       </c>
     </row>
-    <row r="56" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="B56" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="C56" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="D56" s="101">
+    <row r="58" spans="1:9" ht="50.1" customHeight="1">
+      <c r="A58" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="B58" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="C58" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D58" s="121">
         <v>2459</v>
       </c>
-      <c r="E56" s="72"/>
-      <c r="F56" s="1">
+      <c r="E58" s="72"/>
+      <c r="F58" s="1">
         <v>567</v>
       </c>
-      <c r="G56" s="1">
+      <c r="G58" s="1">
         <v>21</v>
       </c>
-      <c r="H56" s="1">
+      <c r="H58" s="1">
         <v>61</v>
       </c>
-      <c r="I56" s="1">
+      <c r="I58" s="1">
         <v>52</v>
       </c>
     </row>
-    <row r="57" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A57" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="B57" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="C57" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="D57" s="101">
+    <row r="59" spans="1:9" ht="50.1" customHeight="1">
+      <c r="A59" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="B59" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="C59" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D59" s="121">
         <v>2444</v>
       </c>
-      <c r="E57" s="71"/>
-      <c r="F57" s="1">
+      <c r="E59" s="71"/>
+      <c r="F59" s="1">
         <v>3035</v>
       </c>
-      <c r="G57" s="1">
+      <c r="G59" s="1">
         <v>0</v>
       </c>
-      <c r="H57" s="1">
+      <c r="H59" s="1">
         <v>61</v>
       </c>
-      <c r="I57" s="1">
+      <c r="I59" s="1">
         <v>81</v>
       </c>
     </row>
-    <row r="58" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A58" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="B58" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="C58" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="D58" s="101">
+    <row r="60" spans="1:9" ht="50.1" customHeight="1">
+      <c r="A60" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="B60" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="C60" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D60" s="121">
         <v>2328</v>
       </c>
-      <c r="E58" s="27"/>
-      <c r="F58" s="1">
+      <c r="E60" s="27"/>
+      <c r="F60" s="1">
         <v>151</v>
-      </c>
-      <c r="G58" s="1">
-        <v>255</v>
-      </c>
-      <c r="H58" s="1">
-        <v>128</v>
-      </c>
-      <c r="I58" s="1">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="59" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A59" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="B59" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="C59" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="D59" s="101">
-        <v>2330</v>
-      </c>
-      <c r="E59" s="29"/>
-      <c r="F59" s="1">
-        <v>1575</v>
-      </c>
-      <c r="G59" s="1">
-        <v>255</v>
-      </c>
-      <c r="H59" s="1">
-        <v>123</v>
-      </c>
-      <c r="I59" s="1">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="60" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A60" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="B60" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="C60" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="D60" s="101">
-        <v>2469</v>
-      </c>
-      <c r="E60" s="31"/>
-      <c r="F60" s="1">
-        <v>165</v>
       </c>
       <c r="G60" s="1">
         <v>255</v>
       </c>
       <c r="H60" s="1">
+        <v>128</v>
+      </c>
+      <c r="I60" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="61" spans="1:9" ht="50.1" customHeight="1">
+      <c r="A61" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="B61" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="C61" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D61" s="121">
+        <v>2330</v>
+      </c>
+      <c r="E61" s="29"/>
+      <c r="F61" s="1">
+        <v>1575</v>
+      </c>
+      <c r="G61" s="1">
+        <v>255</v>
+      </c>
+      <c r="H61" s="1">
+        <v>123</v>
+      </c>
+      <c r="I61" s="1">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="62" spans="1:9" ht="50.1" customHeight="1">
+      <c r="A62" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="B62" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="C62" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D62" s="121">
+        <v>2469</v>
+      </c>
+      <c r="E62" s="31"/>
+      <c r="F62" s="1">
+        <v>165</v>
+      </c>
+      <c r="G62" s="1">
+        <v>255</v>
+      </c>
+      <c r="H62" s="1">
         <v>97</v>
       </c>
-      <c r="I60" s="1">
+      <c r="I62" s="1">
         <v>17</v>
       </c>
     </row>
-    <row r="61" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="B61" s="1" t="s">
+    <row r="63" spans="1:9" ht="50.1" customHeight="1">
+      <c r="A63" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="B63" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="C63" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D63" s="121">
+        <v>2397</v>
+      </c>
+      <c r="E63" s="30"/>
+      <c r="F63" s="1">
+        <v>172</v>
+      </c>
+      <c r="G63" s="1">
+        <v>254</v>
+      </c>
+      <c r="H63" s="1">
+        <v>56</v>
+      </c>
+      <c r="I63" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="64" spans="1:9" ht="50.1" customHeight="1">
+      <c r="A64" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="B64" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="C64" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D64" s="121">
+        <v>2289</v>
+      </c>
+      <c r="E64" s="26"/>
+      <c r="F64" s="1">
+        <v>159</v>
+      </c>
+      <c r="G64" s="1">
+        <v>213</v>
+      </c>
+      <c r="H64" s="1">
+        <v>90</v>
+      </c>
+      <c r="I64" s="1">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="65" spans="1:9" ht="50.1" customHeight="1">
+      <c r="A65" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B65" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="C65" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D65" s="121">
+        <v>2329</v>
+      </c>
+      <c r="E65" s="28"/>
+      <c r="F65" s="1">
+        <v>1788</v>
+      </c>
+      <c r="G65" s="1">
+        <v>246</v>
+      </c>
+      <c r="H65" s="1">
+        <v>24</v>
+      </c>
+      <c r="I65" s="1">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="66" spans="1:9" ht="50.1" customHeight="1">
+      <c r="A66" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="B66" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="C66" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D66" s="121">
+        <v>2256</v>
+      </c>
+      <c r="E66" s="8"/>
+      <c r="F66" s="1">
+        <v>1555</v>
+      </c>
+      <c r="G66" s="1">
+        <v>254</v>
+      </c>
+      <c r="H66" s="1">
+        <v>185</v>
+      </c>
+      <c r="I66" s="1">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="67" spans="1:9" ht="50.1" customHeight="1">
+      <c r="A67" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="B67" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="C67" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D67" s="121">
+        <v>2223</v>
+      </c>
+      <c r="E67" s="91"/>
+      <c r="F67" s="1">
+        <v>1895</v>
+      </c>
+      <c r="G67" s="1">
+        <v>249</v>
+      </c>
+      <c r="H67" s="1">
+        <v>181</v>
+      </c>
+      <c r="I67" s="1">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="68" spans="1:9" ht="50.1" customHeight="1">
+      <c r="A68" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="B68" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="C68" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D68" s="121">
+        <v>2377</v>
+      </c>
+      <c r="E68" s="94"/>
+      <c r="F68" s="1">
+        <v>7520</v>
+      </c>
+      <c r="G68" s="1">
+        <v>238</v>
+      </c>
+      <c r="H68" s="1">
+        <v>191</v>
+      </c>
+      <c r="I68" s="1">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="69" spans="1:9" ht="50.1" customHeight="1">
+      <c r="A69" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="B69" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="C69" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D69" s="121">
+        <v>2293</v>
+      </c>
+      <c r="E69" s="93"/>
+      <c r="F69" s="1">
+        <v>1905</v>
+      </c>
+      <c r="G69" s="1">
+        <v>251</v>
+      </c>
+      <c r="H69" s="1">
+        <v>152</v>
+      </c>
+      <c r="I69" s="1">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="70" spans="1:9" ht="50.1" customHeight="1">
+      <c r="A70" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="B70" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="C70" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D70" s="121">
+        <v>2415</v>
+      </c>
+      <c r="E70" s="95"/>
+      <c r="F70" s="1">
+        <v>2038</v>
+      </c>
+      <c r="G70" s="1">
+        <v>247</v>
+      </c>
+      <c r="H70" s="1">
+        <v>90</v>
+      </c>
+      <c r="I70" s="1">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="71" spans="1:9" ht="50.1" customHeight="1">
+      <c r="A71" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="B71" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="C71" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D71" s="121">
+        <v>2509</v>
+      </c>
+      <c r="E71" s="97"/>
+      <c r="F71" s="1">
+        <v>184</v>
+      </c>
+      <c r="G71" s="1">
+        <v>254</v>
+      </c>
+      <c r="H71" s="1">
         <v>75</v>
       </c>
-      <c r="C61" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="D61" s="101">
-        <v>2397</v>
-      </c>
-      <c r="E61" s="30"/>
-      <c r="F61" s="1">
-        <v>172</v>
-      </c>
-      <c r="G61" s="1">
-        <v>254</v>
-      </c>
-      <c r="H61" s="1">
-        <v>56</v>
-      </c>
-      <c r="I61" s="1">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="62" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A62" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="B62" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="C62" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="D62" s="101">
-        <v>2289</v>
-      </c>
-      <c r="E62" s="26"/>
-      <c r="F62" s="1">
-        <v>159</v>
-      </c>
-      <c r="G62" s="1">
-        <v>213</v>
-      </c>
-      <c r="H62" s="1">
+      <c r="I71" s="1">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="72" spans="1:9" ht="50.1" customHeight="1">
+      <c r="A72" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="I62" s="1">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="63" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A63" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="B63" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="C63" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="D63" s="101">
-        <v>2329</v>
-      </c>
-      <c r="E63" s="28"/>
-      <c r="F63" s="1">
-        <v>1788</v>
-      </c>
-      <c r="G63" s="1">
-        <v>246</v>
-      </c>
-      <c r="H63" s="1">
+      <c r="B72" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="C72" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D72" s="121">
+        <v>2261</v>
+      </c>
+      <c r="E72" s="92"/>
+      <c r="F72" s="1">
+        <v>219</v>
+      </c>
+      <c r="G72" s="1">
+        <v>231</v>
+      </c>
+      <c r="H72" s="1">
+        <v>18</v>
+      </c>
+      <c r="I72" s="1">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="73" spans="1:9" ht="50.1" customHeight="1">
+      <c r="A73" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="B73" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="C73" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D73" s="121">
+        <v>2500</v>
+      </c>
+      <c r="E73" s="96"/>
+      <c r="F73" s="1">
+        <v>2063</v>
+      </c>
+      <c r="G73" s="1">
+        <v>173</v>
+      </c>
+      <c r="H73" s="1">
+        <v>40</v>
+      </c>
+      <c r="I73" s="1">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="74" spans="1:9" ht="50.1" customHeight="1">
+      <c r="A74" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="B74" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="C74" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D74" s="121">
+        <v>2286</v>
+      </c>
+      <c r="E74" s="57"/>
+      <c r="F74" s="1">
+        <v>2073</v>
+      </c>
+      <c r="G74" s="1">
+        <v>200</v>
+      </c>
+      <c r="H74" s="1">
+        <v>149</v>
+      </c>
+      <c r="I74" s="1">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="75" spans="1:9" ht="50.1" customHeight="1">
+      <c r="A75" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="B75" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="C75" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D75" s="121">
+        <v>2288</v>
+      </c>
+      <c r="E75" s="58"/>
+      <c r="F75" s="1">
+        <v>2577</v>
+      </c>
+      <c r="G75" s="1">
+        <v>163</v>
+      </c>
+      <c r="H75" s="1">
+        <v>122</v>
+      </c>
+      <c r="I75" s="1">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="76" spans="1:9" ht="50.1" customHeight="1">
+      <c r="A76" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="B76" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="C76" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D76" s="121">
+        <v>2490</v>
+      </c>
+      <c r="E76" s="61"/>
+      <c r="F76" s="1">
+        <v>520</v>
+      </c>
+      <c r="G76" s="1">
+        <v>136</v>
+      </c>
+      <c r="H76" s="1">
+        <v>99</v>
+      </c>
+      <c r="I76" s="1">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="77" spans="1:9" ht="50.1" customHeight="1">
+      <c r="A77" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="B77" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="C77" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D77" s="121">
+        <v>2380</v>
+      </c>
+      <c r="E77" s="59"/>
+      <c r="F77" s="1">
+        <v>2613</v>
+      </c>
+      <c r="G77" s="1">
+        <v>109</v>
+      </c>
+      <c r="H77" s="1">
         <v>24</v>
       </c>
-      <c r="I63" s="1">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="64" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A64" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="B64" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="C64" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="D64" s="101">
-        <v>2256</v>
-      </c>
-      <c r="E64" s="8"/>
-      <c r="F64" s="1">
-        <v>1555</v>
-      </c>
-      <c r="G64" s="1">
-        <v>254</v>
-      </c>
-      <c r="H64" s="1">
-        <v>185</v>
-      </c>
-      <c r="I64" s="1">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="65" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A65" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="B65" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="C65" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="D65" s="101">
-        <v>2223</v>
-      </c>
-      <c r="E65" s="91"/>
-      <c r="F65" s="1">
-        <v>1895</v>
-      </c>
-      <c r="G65" s="1">
-        <v>249</v>
-      </c>
-      <c r="H65" s="1">
-        <v>181</v>
-      </c>
-      <c r="I65" s="1">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="66" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A66" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="B66" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="C66" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="D66" s="101">
-        <v>2377</v>
-      </c>
-      <c r="E66" s="94"/>
-      <c r="F66" s="1">
-        <v>7520</v>
-      </c>
-      <c r="G66" s="1">
-        <v>238</v>
-      </c>
-      <c r="H66" s="1">
-        <v>191</v>
-      </c>
-      <c r="I66" s="1">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="67" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A67" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="B67" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="C67" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="D67" s="101">
-        <v>2293</v>
-      </c>
-      <c r="E67" s="93"/>
-      <c r="F67" s="1">
-        <v>1905</v>
-      </c>
-      <c r="G67" s="1">
-        <v>251</v>
-      </c>
-      <c r="H67" s="1">
-        <v>152</v>
-      </c>
-      <c r="I67" s="1">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="68" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A68" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="B68" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="C68" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="D68" s="101">
-        <v>2415</v>
-      </c>
-      <c r="E68" s="95"/>
-      <c r="F68" s="1">
-        <v>2038</v>
-      </c>
-      <c r="G68" s="1">
-        <v>247</v>
-      </c>
-      <c r="H68" s="1">
-        <v>90</v>
-      </c>
-      <c r="I68" s="1">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="69" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A69" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="B69" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="C69" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="D69" s="101">
-        <v>2509</v>
-      </c>
-      <c r="E69" s="97"/>
-      <c r="F69" s="1">
-        <v>184</v>
-      </c>
-      <c r="G69" s="1">
-        <v>254</v>
-      </c>
-      <c r="H69" s="1">
-        <v>75</v>
-      </c>
-      <c r="I69" s="1">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="70" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A70" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="B70" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="C70" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="D70" s="101">
-        <v>2261</v>
-      </c>
-      <c r="E70" s="92"/>
-      <c r="F70" s="1">
-        <v>219</v>
-      </c>
-      <c r="G70" s="1">
-        <v>231</v>
-      </c>
-      <c r="H70" s="1">
-        <v>18</v>
-      </c>
-      <c r="I70" s="1">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="71" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A71" s="1" t="s">
+      <c r="I77" s="1">
         <v>115</v>
       </c>
-      <c r="B71" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="C71" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="D71" s="101">
-        <v>2500</v>
-      </c>
-      <c r="E71" s="96"/>
-      <c r="F71" s="1">
-        <v>2063</v>
-      </c>
-      <c r="G71" s="1">
-        <v>173</v>
-      </c>
-      <c r="H71" s="1">
+    </row>
+    <row r="78" spans="1:9" ht="50.1" customHeight="1">
+      <c r="A78" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="B78" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="C78" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D78" s="121">
+        <v>2254</v>
+      </c>
+      <c r="E78" s="56"/>
+      <c r="F78" s="1">
+        <v>268</v>
+      </c>
+      <c r="G78" s="1">
+        <v>92</v>
+      </c>
+      <c r="H78" s="1">
         <v>40</v>
       </c>
-      <c r="I71" s="1">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="72" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A72" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="B72" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="C72" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="D72" s="101">
-        <v>2286</v>
-      </c>
-      <c r="E72" s="57"/>
-      <c r="F72" s="1">
-        <v>2073</v>
-      </c>
-      <c r="G72" s="1">
-        <v>200</v>
-      </c>
-      <c r="H72" s="1">
-        <v>149</v>
-      </c>
-      <c r="I72" s="1">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="73" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A73" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="B73" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="C73" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="D73" s="101">
-        <v>2288</v>
-      </c>
-      <c r="E73" s="58"/>
-      <c r="F73" s="1">
-        <v>2577</v>
-      </c>
-      <c r="G73" s="1">
-        <v>163</v>
-      </c>
-      <c r="H73" s="1">
-        <v>122</v>
-      </c>
-      <c r="I73" s="1">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="74" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A74" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="B74" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="C74" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="D74" s="101">
-        <v>2490</v>
-      </c>
-      <c r="E74" s="61"/>
-      <c r="F74" s="1">
-        <v>520</v>
-      </c>
-      <c r="G74" s="1">
-        <v>136</v>
-      </c>
-      <c r="H74" s="1">
+      <c r="I78" s="1">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="79" spans="1:9" ht="50.1" customHeight="1">
+      <c r="A79" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="B79" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="C79" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D79" s="121">
+        <v>2381</v>
+      </c>
+      <c r="E79" s="60"/>
+      <c r="F79" s="1">
+        <v>269</v>
+      </c>
+      <c r="G79" s="1">
+        <v>84</v>
+      </c>
+      <c r="H79" s="1">
+        <v>43</v>
+      </c>
+      <c r="I79" s="1">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="80" spans="1:9" ht="50.1" customHeight="1">
+      <c r="A80" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="I74" s="1">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="75" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A75" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="B75" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="C75" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="D75" s="101">
-        <v>2380</v>
-      </c>
-      <c r="E75" s="59"/>
-      <c r="F75" s="1">
-        <v>2613</v>
-      </c>
-      <c r="G75" s="1">
-        <v>109</v>
-      </c>
-      <c r="H75" s="1">
-        <v>24</v>
-      </c>
-      <c r="I75" s="1">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="76" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A76" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="B76" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="C76" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="D76" s="101">
-        <v>2254</v>
-      </c>
-      <c r="E76" s="56"/>
-      <c r="F76" s="1">
-        <v>268</v>
-      </c>
-      <c r="G76" s="1">
-        <v>92</v>
-      </c>
-      <c r="H76" s="1">
-        <v>40</v>
-      </c>
-      <c r="I76" s="1">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="77" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A77" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="B77" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="C77" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="D77" s="101">
-        <v>2381</v>
-      </c>
-      <c r="E77" s="60"/>
-      <c r="F77" s="1">
-        <v>269</v>
-      </c>
-      <c r="G77" s="1">
-        <v>84</v>
-      </c>
-      <c r="H77" s="1">
+      <c r="B80" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="C80" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D80" s="121">
+        <v>2427</v>
+      </c>
+      <c r="E80" s="47"/>
+      <c r="F80" s="1">
+        <v>2756</v>
+      </c>
+      <c r="G80" s="1">
+        <v>21</v>
+      </c>
+      <c r="H80" s="1">
+        <v>30</v>
+      </c>
+      <c r="I80" s="1">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="81" spans="1:9" ht="50.1" customHeight="1">
+      <c r="A81" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="B81" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="C81" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D81" s="121">
+        <v>2266</v>
+      </c>
+      <c r="E81" s="52"/>
+      <c r="F81" s="1">
+        <v>199</v>
+      </c>
+      <c r="G81" s="1">
+        <v>226</v>
+      </c>
+      <c r="H81" s="1">
+        <v>3</v>
+      </c>
+      <c r="I81" s="1">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="82" spans="1:9" ht="50.1" customHeight="1">
+      <c r="A82" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="B82" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="C82" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D82" s="121">
+        <v>2420</v>
+      </c>
+      <c r="E82" s="55"/>
+      <c r="F82" s="1">
+        <v>1795</v>
+      </c>
+      <c r="G82" s="1">
+        <v>220</v>
+      </c>
+      <c r="H82" s="1">
+        <v>19</v>
+      </c>
+      <c r="I82" s="1">
         <v>43</v>
       </c>
-      <c r="I77" s="1">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="78" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A78" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="B78" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="C78" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="D78" s="101">
-        <v>2427</v>
-      </c>
-      <c r="E78" s="47"/>
-      <c r="F78" s="1">
-        <v>2756</v>
-      </c>
-      <c r="G78" s="1">
-        <v>21</v>
-      </c>
-      <c r="H78" s="1">
-        <v>30</v>
-      </c>
-      <c r="I78" s="1">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="79" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A79" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="B79" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="C79" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="D79" s="101">
-        <v>2266</v>
-      </c>
-      <c r="E79" s="52"/>
-      <c r="F79" s="1">
-        <v>199</v>
-      </c>
-      <c r="G79" s="1">
-        <v>226</v>
-      </c>
-      <c r="H79" s="1">
-        <v>3</v>
-      </c>
-      <c r="I79" s="1">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="80" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A80" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="B80" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="C80" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="D80" s="101">
-        <v>2420</v>
-      </c>
-      <c r="E80" s="55"/>
-      <c r="F80" s="1">
-        <v>1795</v>
-      </c>
-      <c r="G80" s="1">
-        <v>220</v>
-      </c>
-      <c r="H80" s="1">
-        <v>19</v>
-      </c>
-      <c r="I80" s="1">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="81" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A81" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="B81" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="C81" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="D81" s="101">
+    </row>
+    <row r="83" spans="1:9" ht="50.1" customHeight="1">
+      <c r="A83" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="B83" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="C83" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D83" s="121">
         <v>2263</v>
       </c>
-      <c r="E81" s="51"/>
-      <c r="F81" s="1">
+      <c r="E83" s="51"/>
+      <c r="F83" s="1">
         <v>206</v>
       </c>
-      <c r="G81" s="1">
+      <c r="G83" s="1">
         <v>212</v>
       </c>
-      <c r="H81" s="1">
+      <c r="H83" s="1">
         <v>1</v>
-      </c>
-      <c r="I81" s="1">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="82" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A82" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="B82" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="C82" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="D82" s="101">
-        <v>2249</v>
-      </c>
-      <c r="E82" s="49"/>
-      <c r="F82" s="1">
-        <v>7420</v>
-      </c>
-      <c r="G82" s="1">
-        <v>163</v>
-      </c>
-      <c r="H82" s="1">
-        <v>22</v>
-      </c>
-      <c r="I82" s="1">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="83" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A83" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="B83" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="C83" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="D83" s="101">
-        <v>2334</v>
-      </c>
-      <c r="E83" s="53"/>
-      <c r="F83" s="1">
-        <v>7622</v>
-      </c>
-      <c r="G83" s="1">
-        <v>154</v>
-      </c>
-      <c r="H83" s="1">
-        <v>29</v>
       </c>
       <c r="I83" s="1">
         <v>41</v>
       </c>
     </row>
-    <row r="84" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:9" ht="50.1" customHeight="1">
       <c r="A84" s="1" t="s">
-        <v>58</v>
+        <v>104</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>73</v>
+        <v>101</v>
       </c>
       <c r="C84" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="D84" s="101">
+        <v>11</v>
+      </c>
+      <c r="D84" s="121">
+        <v>2249</v>
+      </c>
+      <c r="E84" s="49"/>
+      <c r="F84" s="1">
+        <v>7420</v>
+      </c>
+      <c r="G84" s="1">
+        <v>163</v>
+      </c>
+      <c r="H84" s="1">
+        <v>22</v>
+      </c>
+      <c r="I84" s="1">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="85" spans="1:9" ht="50.1" customHeight="1">
+      <c r="A85" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="B85" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="C85" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D85" s="121">
+        <v>2334</v>
+      </c>
+      <c r="E85" s="53"/>
+      <c r="F85" s="1">
+        <v>7622</v>
+      </c>
+      <c r="G85" s="1">
+        <v>154</v>
+      </c>
+      <c r="H85" s="1">
+        <v>29</v>
+      </c>
+      <c r="I85" s="1">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="86" spans="1:9" ht="50.1" customHeight="1">
+      <c r="A86" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="B86" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="C86" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D86" s="121">
         <v>2252</v>
       </c>
-      <c r="E84" s="50"/>
-      <c r="F84" s="1">
+      <c r="E86" s="50"/>
+      <c r="F86" s="1">
         <v>208</v>
       </c>
-      <c r="G84" s="1">
+      <c r="G86" s="1">
         <v>142</v>
       </c>
-      <c r="H84" s="1">
+      <c r="H86" s="1">
         <v>20</v>
       </c>
-      <c r="I84" s="1">
+      <c r="I86" s="1">
         <v>64</v>
       </c>
     </row>
-    <row r="85" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A85" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="B85" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="C85" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="D85" s="101">
+    <row r="87" spans="1:9" ht="50.1" customHeight="1">
+      <c r="A87" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="B87" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="C87" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D87" s="121">
         <v>2225</v>
       </c>
-      <c r="E85" s="48"/>
-      <c r="F85" s="1">
+      <c r="E87" s="48"/>
+      <c r="F87" s="1">
         <v>209</v>
       </c>
-      <c r="G85" s="1">
+      <c r="G87" s="1">
         <v>116</v>
       </c>
-      <c r="H85" s="1">
+      <c r="H87" s="1">
         <v>33</v>
       </c>
-      <c r="I85" s="1">
+      <c r="I87" s="1">
         <v>60</v>
       </c>
     </row>
-    <row r="86" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A86" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="B86" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="C86" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="D86" s="101">
+    <row r="88" spans="1:9" ht="50.1" customHeight="1">
+      <c r="A88" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="B88" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="C88" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D88" s="121">
         <v>2376</v>
       </c>
-      <c r="E86" s="54"/>
-      <c r="F86" s="1">
+      <c r="E88" s="54"/>
+      <c r="F88" s="1">
         <v>7428</v>
       </c>
-      <c r="G86" s="1">
+      <c r="G88" s="1">
         <v>110</v>
       </c>
-      <c r="H86" s="1">
+      <c r="H88" s="1">
         <v>40</v>
       </c>
-      <c r="I86" s="1">
+      <c r="I88" s="1">
         <v>60</v>
       </c>
     </row>
-    <row r="87" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A87" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="B87" s="1" t="s">
-        <v>121</v>
-      </c>
-      <c r="C87" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="D87" s="101">
+    <row r="89" spans="1:9" ht="48" customHeight="1">
+      <c r="A89" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="B89" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="C89" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D89" s="121">
         <v>2297</v>
       </c>
-      <c r="E87" s="99"/>
-      <c r="F87" s="1" t="s">
-        <v>122</v>
-      </c>
-      <c r="G87" s="1">
+      <c r="E89" s="99"/>
+      <c r="F89" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="G89" s="1">
         <v>255</v>
       </c>
-      <c r="H87" s="1">
+      <c r="H89" s="1">
         <v>255</v>
       </c>
-      <c r="I87" s="1">
+      <c r="I89" s="1">
         <v>255</v>
       </c>
     </row>
-    <row r="88" spans="1:9" ht="48.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A88" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B88" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="C88" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="D88" s="101">
+    <row r="90" spans="1:9" ht="48.75" customHeight="1">
+      <c r="A90" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="B90" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="C90" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D90" s="121">
         <v>2264</v>
       </c>
-      <c r="E88" s="9"/>
-      <c r="F88" s="1">
+      <c r="E90" s="9"/>
+      <c r="F90" s="1">
         <v>7401</v>
       </c>
-      <c r="G88" s="1">
+      <c r="G90" s="1">
         <v>248</v>
       </c>
-      <c r="H88" s="1">
+      <c r="H90" s="1">
         <v>224</v>
       </c>
-      <c r="I88" s="1">
+      <c r="I90" s="1">
         <v>162</v>
       </c>
     </row>
-    <row r="89" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A89" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B89" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="C89" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="D89" s="101">
+    <row r="91" spans="1:9" ht="50.1" customHeight="1">
+      <c r="A91" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="B91" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="C91" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D91" s="121">
         <v>2325</v>
       </c>
-      <c r="E89" s="10"/>
-      <c r="F89" s="1">
+      <c r="E91" s="10"/>
+      <c r="F91" s="1">
         <v>100</v>
       </c>
-      <c r="G89" s="1">
+      <c r="G91" s="1">
         <v>249</v>
       </c>
-      <c r="H89" s="1">
+      <c r="H91" s="1">
         <v>235</v>
       </c>
-      <c r="I89" s="1">
+      <c r="I91" s="1">
         <v>89</v>
       </c>
     </row>
-    <row r="90" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A90" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B90" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="C90" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="D90" s="101">
+    <row r="92" spans="1:9" ht="50.1" customHeight="1">
+      <c r="A92" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="B92" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="C92" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D92" s="121">
         <v>2235</v>
       </c>
-      <c r="E90" s="6"/>
-      <c r="F90" s="1">
+      <c r="E92" s="6"/>
+      <c r="F92" s="1">
         <v>102</v>
       </c>
-      <c r="G90" s="1">
+      <c r="G92" s="1">
         <v>251</v>
       </c>
-      <c r="H90" s="1">
+      <c r="H92" s="1">
         <v>227</v>
       </c>
-      <c r="I90" s="1">
+      <c r="I92" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="91" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A91" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="B91" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="C91" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="D91" s="101">
+    <row r="93" spans="1:9" ht="50.1" customHeight="1">
+      <c r="A93" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="B93" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="C93" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D93" s="121">
         <v>2399</v>
       </c>
-      <c r="E91" s="12"/>
-      <c r="F91" s="1">
+      <c r="E93" s="12"/>
+      <c r="F93" s="1">
         <v>726</v>
       </c>
-      <c r="G91" s="1">
+      <c r="G93" s="1">
         <v>227</v>
       </c>
-      <c r="H91" s="1">
+      <c r="H93" s="1">
         <v>193</v>
       </c>
-      <c r="I91" s="1">
+      <c r="I93" s="1">
         <v>157</v>
       </c>
     </row>
-    <row r="92" spans="1:9" ht="49.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A92" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B92" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="C92" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="D92" s="101">
+    <row r="94" spans="1:9" ht="49.5" customHeight="1">
+      <c r="A94" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="B94" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="C94" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D94" s="121">
         <v>2247</v>
       </c>
-      <c r="E92" s="8"/>
-      <c r="F92" s="1">
+      <c r="E94" s="8"/>
+      <c r="F94" s="1">
         <v>1555</v>
       </c>
-      <c r="G92" s="1">
+      <c r="G94" s="1">
         <v>254</v>
       </c>
-      <c r="H92" s="1">
+      <c r="H94" s="1">
         <v>185</v>
       </c>
-      <c r="I92" s="1">
+      <c r="I94" s="1">
         <v>140</v>
       </c>
     </row>
-    <row r="93" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A93" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B93" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="C93" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="D93" s="101">
+    <row r="95" spans="1:9" ht="50.1" customHeight="1">
+      <c r="A95" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="B95" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="C95" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D95" s="121">
         <v>2242</v>
       </c>
-      <c r="E93" s="7"/>
-      <c r="F93" s="1">
+      <c r="E95" s="7"/>
+      <c r="F95" s="1">
         <v>116</v>
       </c>
-      <c r="G93" s="1">
+      <c r="G95" s="1">
         <v>253</v>
       </c>
-      <c r="H93" s="1">
+      <c r="H95" s="1">
         <v>206</v>
       </c>
-      <c r="I93" s="1">
+      <c r="I95" s="1">
         <v>1</v>
       </c>
     </row>
-    <row r="94" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A94" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B94" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="C94" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="D94" s="101">
+    <row r="96" spans="1:9" ht="50.1" customHeight="1">
+      <c r="A96" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="B96" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="C96" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D96" s="121">
         <v>2216</v>
       </c>
-      <c r="E94" s="4"/>
-      <c r="F94" s="1">
+      <c r="E96" s="4"/>
+      <c r="F96" s="1">
         <v>1225</v>
-      </c>
-      <c r="G94" s="1">
-        <v>255</v>
-      </c>
-      <c r="H94" s="1">
-        <v>200</v>
-      </c>
-      <c r="I94" s="1">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="95" spans="1:9" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A95" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="B95" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="C95" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="D95" s="101">
-        <v>2466</v>
-      </c>
-      <c r="E95" s="13"/>
-      <c r="F95" s="1">
-        <v>7548</v>
-      </c>
-      <c r="G95" s="1">
-        <v>255</v>
-      </c>
-      <c r="H95" s="1">
-        <v>199</v>
-      </c>
-      <c r="I95" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="96" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A96" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="B96" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="C96" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="D96" s="101">
-        <v>2558</v>
-      </c>
-      <c r="E96" s="15"/>
-      <c r="F96" s="1">
-        <v>1235</v>
       </c>
       <c r="G96" s="1">
         <v>255</v>
       </c>
       <c r="H96" s="1">
-        <v>183</v>
+        <v>200</v>
       </c>
       <c r="I96" s="1">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="97" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="97" spans="1:9" ht="45" customHeight="1">
       <c r="A97" s="1" t="s">
-        <v>8</v>
+        <v>120</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>76</v>
+        <v>113</v>
       </c>
       <c r="C97" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="D97" s="101">
-        <v>2213</v>
-      </c>
-      <c r="E97" s="3"/>
+        <v>11</v>
+      </c>
+      <c r="D97" s="121">
+        <v>2466</v>
+      </c>
+      <c r="E97" s="13"/>
       <c r="F97" s="1">
-        <v>137</v>
+        <v>7548</v>
       </c>
       <c r="G97" s="1">
         <v>255</v>
       </c>
       <c r="H97" s="1">
+        <v>199</v>
+      </c>
+      <c r="I97" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="1:9" ht="48" customHeight="1">
+      <c r="A98" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="B98" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="C98" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D98" s="121">
+        <v>2558</v>
+      </c>
+      <c r="E98" s="15"/>
+      <c r="F98" s="1">
+        <v>1235</v>
+      </c>
+      <c r="G98" s="1">
+        <v>255</v>
+      </c>
+      <c r="H98" s="1">
+        <v>183</v>
+      </c>
+      <c r="I98" s="1">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="99" spans="1:9" ht="50.1" customHeight="1">
+      <c r="A99" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="B99" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="C99" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D99" s="121">
+        <v>2213</v>
+      </c>
+      <c r="E99" s="3"/>
+      <c r="F99" s="1">
+        <v>137</v>
+      </c>
+      <c r="G99" s="1">
+        <v>255</v>
+      </c>
+      <c r="H99" s="1">
         <v>163</v>
       </c>
-      <c r="I97" s="1">
+      <c r="I99" s="1">
         <v>2</v>
       </c>
     </row>
-    <row r="98" spans="1:9" ht="49.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A98" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="B98" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="C98" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="D98" s="101">
+    <row r="100" spans="1:9" ht="49.5" customHeight="1">
+      <c r="A100" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="B100" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="C100" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D100" s="121">
         <v>2586</v>
       </c>
-      <c r="E98" s="16"/>
-      <c r="F98" s="1">
+      <c r="E100" s="16"/>
+      <c r="F100" s="1">
         <v>7563</v>
       </c>
-      <c r="G98" s="1">
+      <c r="G100" s="1">
         <v>218</v>
       </c>
-      <c r="H98" s="1">
+      <c r="H100" s="1">
         <v>154</v>
       </c>
-      <c r="I98" s="1">
+      <c r="I100" s="1">
         <v>29</v>
       </c>
     </row>
-    <row r="99" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A99" s="1" t="s">
+    <row r="101" spans="1:9" ht="50.1" customHeight="1">
+      <c r="A101" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="B101" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="C101" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D101" s="121">
+        <v>2471</v>
+      </c>
+      <c r="E101" s="14"/>
+      <c r="F101" s="1">
+        <v>117</v>
+      </c>
+      <c r="G101" s="1">
+        <v>205</v>
+      </c>
+      <c r="H101" s="1">
+        <v>151</v>
+      </c>
+      <c r="I101" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="1:9" ht="50.1" customHeight="1">
+      <c r="A102" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="B102" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="C102" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D102" s="121">
+        <v>2212</v>
+      </c>
+      <c r="E102" s="2"/>
+      <c r="F102" s="1">
+        <v>7564</v>
+      </c>
+      <c r="G102" s="1">
+        <v>225</v>
+      </c>
+      <c r="H102" s="1">
+        <v>137</v>
+      </c>
+      <c r="I102" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="103" spans="1:9" ht="45.75" customHeight="1">
+      <c r="A103" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="B103" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="C103" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D103" s="121">
+        <v>2333</v>
+      </c>
+      <c r="E103" s="11"/>
+      <c r="F103" s="1">
+        <v>1255</v>
+      </c>
+      <c r="G103" s="1">
+        <v>176</v>
+      </c>
+      <c r="H103" s="1">
+        <v>132</v>
+      </c>
+      <c r="I103" s="1">
         <v>20</v>
       </c>
-      <c r="B99" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="C99" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="D99" s="101">
-        <v>2471</v>
-      </c>
-      <c r="E99" s="14"/>
-      <c r="F99" s="1">
-        <v>117</v>
-      </c>
-      <c r="G99" s="1">
-        <v>205</v>
-      </c>
-      <c r="H99" s="1">
-        <v>151</v>
-      </c>
-      <c r="I99" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="100" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A100" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B100" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="C100" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="D100" s="101">
-        <v>2212</v>
-      </c>
-      <c r="E100" s="2"/>
-      <c r="F100" s="1">
-        <v>7564</v>
-      </c>
-      <c r="G100" s="1">
-        <v>225</v>
-      </c>
-      <c r="H100" s="1">
-        <v>137</v>
-      </c>
-      <c r="I100" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101" spans="1:9" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A101" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="B101" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="C101" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="D101" s="101">
-        <v>2333</v>
-      </c>
-      <c r="E101" s="11"/>
-      <c r="F101" s="1">
-        <v>1255</v>
-      </c>
-      <c r="G101" s="1">
-        <v>176</v>
-      </c>
-      <c r="H101" s="1">
-        <v>132</v>
-      </c>
-      <c r="I101" s="1">
-        <v>20</v>
-      </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="imE4++UC4zxO3Bg9oJL60s6T0zI1soCzpxP6G684zL8KZq7vklLWzsvMnQ+NO5IFkYPPmiTLZ5P7HQP2/vvjwQ==" saltValue="P5Mo0UM1eMqbf7G0i4kGsg==" spinCount="100000" sheet="1" objects="1" scenarios="1" sort="0" autoFilter="0"/>
+  <sheetProtection sort="0" autoFilter="0"/>
   <protectedRanges>
-    <protectedRange sqref="A1:I101" name="AllowSortFilter"/>
+    <protectedRange sqref="A1:I103" name="AllowSortFilter"/>
   </protectedRanges>
-  <autoFilter ref="A1:I101" xr:uid="{FF431DED-CC07-445B-98CD-FA1799BBCA91}"/>
+  <autoFilter ref="A1:I103" xr:uid="{FF431DED-CC07-445B-98CD-FA1799BBCA91}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="204" verticalDpi="196" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{297DD2E9-CB7D-4550-AA15-AC1F9F166D91}">
+  <dimension ref="A1:I18"/>
+  <sheetFormatPr defaultColWidth="0" defaultRowHeight="15" zeroHeight="1"/>
+  <cols>
+    <col min="1" max="1" width="20.7109375" style="1" customWidth="1"/>
+    <col min="2" max="2" width="17.7109375" style="1" customWidth="1"/>
+    <col min="3" max="3" width="17.5703125" style="1" customWidth="1"/>
+    <col min="4" max="4" width="19.7109375" style="104" customWidth="1"/>
+    <col min="5" max="5" width="50.7109375" style="1" customWidth="1"/>
+    <col min="6" max="6" width="17.7109375" style="1" customWidth="1"/>
+    <col min="7" max="9" width="8.85546875" style="1" customWidth="1"/>
+    <col min="10" max="16384" width="8.85546875" style="1" hidden="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" s="5" customFormat="1" ht="50.1" customHeight="1">
+      <c r="A1" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="105" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="5" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" ht="50.1" customHeight="1">
+      <c r="A2" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="D2" s="104">
+        <v>3951</v>
+      </c>
+      <c r="E2" s="106"/>
+      <c r="F2" s="1">
+        <v>2205</v>
+      </c>
+      <c r="G2" s="1">
+        <v>138</v>
+      </c>
+      <c r="H2" s="1">
+        <v>177</v>
+      </c>
+      <c r="I2" s="1">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" ht="50.1" customHeight="1">
+      <c r="A3" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="D3" s="104">
+        <v>3612</v>
+      </c>
+      <c r="E3" s="37"/>
+      <c r="F3" s="1">
+        <v>7686</v>
+      </c>
+      <c r="G3" s="1">
+        <v>27</v>
+      </c>
+      <c r="H3" s="1">
+        <v>78</v>
+      </c>
+      <c r="I3" s="1">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" ht="50.1" customHeight="1">
+      <c r="A4" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="D4" s="104">
+        <v>3344</v>
+      </c>
+      <c r="E4" s="32"/>
+      <c r="F4" s="1">
+        <v>296</v>
+      </c>
+      <c r="G4" s="1">
+        <v>8</v>
+      </c>
+      <c r="H4" s="1">
+        <v>27</v>
+      </c>
+      <c r="I4" s="1">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" ht="50.1" customHeight="1">
+      <c r="A5" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="D5" s="104">
+        <v>142</v>
+      </c>
+      <c r="E5" s="109"/>
+      <c r="F5" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="G5" s="1">
+        <v>178</v>
+      </c>
+      <c r="H5" s="1">
+        <v>178</v>
+      </c>
+      <c r="I5" s="1">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" ht="50.1" customHeight="1">
+      <c r="A6" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="D6" s="104">
+        <v>672</v>
+      </c>
+      <c r="E6" s="107"/>
+      <c r="F6" s="1">
+        <v>7535</v>
+      </c>
+      <c r="G6" s="1">
+        <v>184</v>
+      </c>
+      <c r="H6" s="1">
+        <v>177</v>
+      </c>
+      <c r="I6" s="1">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" ht="50.1" customHeight="1">
+      <c r="A7" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="D7" s="104">
+        <v>108</v>
+      </c>
+      <c r="E7" s="110"/>
+      <c r="F7" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="G7" s="1">
+        <v>137</v>
+      </c>
+      <c r="H7" s="1">
+        <v>138</v>
+      </c>
+      <c r="I7" s="1">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" ht="50.1" customHeight="1">
+      <c r="A8" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="D8" s="104">
+        <v>111</v>
+      </c>
+      <c r="E8" s="111"/>
+      <c r="F8" s="1">
+        <v>416</v>
+      </c>
+      <c r="G8" s="1">
+        <v>127</v>
+      </c>
+      <c r="H8" s="1">
+        <v>126</v>
+      </c>
+      <c r="I8" s="1">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" ht="50.1" customHeight="1">
+      <c r="A9" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="D9" s="104">
+        <v>6031</v>
+      </c>
+      <c r="E9" s="112"/>
+      <c r="F9" s="1">
+        <v>389</v>
+      </c>
+      <c r="G9" s="1">
+        <v>208</v>
+      </c>
+      <c r="H9" s="1">
+        <v>222</v>
+      </c>
+      <c r="I9" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" ht="50.1" customHeight="1">
+      <c r="A10" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="D10" s="104">
+        <v>5912</v>
+      </c>
+      <c r="E10" s="68"/>
+      <c r="F10" s="1">
+        <v>376</v>
+      </c>
+      <c r="G10" s="1">
+        <v>131</v>
+      </c>
+      <c r="H10" s="1">
+        <v>188</v>
+      </c>
+      <c r="I10" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" ht="50.1" customHeight="1">
+      <c r="A11" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="D11" s="104">
+        <v>546</v>
+      </c>
+      <c r="E11" s="113"/>
+      <c r="F11" s="1">
+        <v>7753</v>
+      </c>
+      <c r="G11" s="1">
+        <v>196</v>
+      </c>
+      <c r="H11" s="1">
+        <v>161</v>
+      </c>
+      <c r="I11" s="1">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" ht="50.1" customHeight="1">
+      <c r="A12" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="D12" s="104">
+        <v>5664</v>
+      </c>
+      <c r="E12" s="108"/>
+      <c r="F12" s="1">
+        <v>5625</v>
+      </c>
+      <c r="G12" s="1">
+        <v>114</v>
+      </c>
+      <c r="H12" s="1">
+        <v>131</v>
+      </c>
+      <c r="I12" s="1">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" ht="50.1" customHeight="1">
+      <c r="A13" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="D13" s="104">
+        <v>1300</v>
+      </c>
+      <c r="E13" s="114"/>
+      <c r="F13" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="G13" s="1">
+        <v>255</v>
+      </c>
+      <c r="H13" s="1">
+        <v>72</v>
+      </c>
+      <c r="I13" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" ht="50.1" customHeight="1">
+      <c r="A14" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="D14" s="104">
+        <v>2152</v>
+      </c>
+      <c r="E14" s="115"/>
+      <c r="F14" s="1">
+        <v>197</v>
+      </c>
+      <c r="G14" s="1">
+        <v>241</v>
+      </c>
+      <c r="H14" s="1">
+        <v>154</v>
+      </c>
+      <c r="I14" s="1">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" ht="50.1" customHeight="1">
+      <c r="A15" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="D15" s="104">
+        <v>2711</v>
+      </c>
+      <c r="E15" s="116"/>
+      <c r="F15" s="1">
+        <v>7651</v>
+      </c>
+      <c r="G15" s="1">
+        <v>111</v>
+      </c>
+      <c r="H15" s="1">
+        <v>38</v>
+      </c>
+      <c r="I15" s="1">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" ht="50.1" customHeight="1">
+      <c r="A16" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="D16" s="104">
+        <v>1703</v>
+      </c>
+      <c r="E16" s="117"/>
+      <c r="F16" s="1">
+        <v>485</v>
+      </c>
+      <c r="G16" s="1">
+        <v>231</v>
+      </c>
+      <c r="H16" s="1">
+        <v>22</v>
+      </c>
+      <c r="I16" s="1">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" ht="50.1" customHeight="1">
+      <c r="A17" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="D17" s="104">
+        <v>1904</v>
+      </c>
+      <c r="E17" s="51"/>
+      <c r="F17" s="1">
+        <v>186</v>
+      </c>
+      <c r="G17" s="1">
+        <v>212</v>
+      </c>
+      <c r="H17" s="1">
+        <v>1</v>
+      </c>
+      <c r="I17" s="1">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" ht="50.1" customHeight="1">
+      <c r="A18" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="D18" s="104">
+        <v>2224</v>
+      </c>
+      <c r="E18" s="118"/>
+      <c r="F18" s="1">
+        <v>7638</v>
+      </c>
+      <c r="G18" s="1">
+        <v>133</v>
+      </c>
+      <c r="H18" s="1">
+        <v>39</v>
+      </c>
+      <c r="I18" s="1">
+        <v>64</v>
+      </c>
+    </row>
+  </sheetData>
+  <sheetProtection sort="0" autoFilter="0"/>
+  <protectedRanges>
+    <protectedRange sqref="A1:I18" name="AllowSortFilter"/>
+  </protectedRanges>
+  <autoFilter ref="A1:I1" xr:uid="{297DD2E9-CB7D-4550-AA15-AC1F9F166D91}"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F92CA703-6419-455B-A827-6E88C97AB8DB}">
+  <dimension ref="A1:I2"/>
+  <sheetFormatPr defaultColWidth="0" defaultRowHeight="15" zeroHeight="1"/>
+  <cols>
+    <col min="1" max="1" width="20.7109375" style="1" customWidth="1"/>
+    <col min="2" max="2" width="17.7109375" style="1" customWidth="1"/>
+    <col min="3" max="3" width="17.5703125" style="1" customWidth="1"/>
+    <col min="4" max="4" width="19.7109375" style="1" customWidth="1"/>
+    <col min="5" max="5" width="50.7109375" style="1" customWidth="1"/>
+    <col min="6" max="6" width="17.7109375" style="1" customWidth="1"/>
+    <col min="7" max="9" width="8.85546875" style="1" customWidth="1"/>
+    <col min="10" max="16384" width="8.85546875" style="1" hidden="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" s="5" customFormat="1" ht="50.1" customHeight="1">
+      <c r="A1" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="5" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" ht="50.1" customHeight="1">
+      <c r="A2" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="D2" s="1">
+        <v>1095</v>
+      </c>
+      <c r="E2" s="119"/>
+      <c r="F2" s="1">
+        <v>638</v>
+      </c>
+      <c r="G2" s="1">
+        <v>0</v>
+      </c>
+      <c r="H2" s="1">
+        <v>173</v>
+      </c>
+      <c r="I2" s="1">
+        <v>215</v>
+      </c>
+    </row>
+  </sheetData>
+  <sheetProtection sort="0" autoFilter="0"/>
+  <protectedRanges>
+    <protectedRange sqref="A1:I2" name="AllowSortFilter"/>
+  </protectedRanges>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100A1C7DD37AE641E4B9B3FD2F75B2D99BC" ma:contentTypeVersion="10" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="6b9cb41f595aff4764e09aef2b23c1ed">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="ea7a09a4-fe73-437e-8a86-996460e9b058" xmlns:ns3="a2b9d960-66d6-4e1d-a64a-950bc94b8bb0" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="daad8a4a6daff5298e6b89d91afce8e3" ns2:_="" ns3:_="">
+    <xsd:import namespace="ea7a09a4-fe73-437e-8a86-996460e9b058"/>
+    <xsd:import namespace="a2b9d960-66d6-4e1d-a64a-950bc94b8bb0"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
+                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
+                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="ea7a09a4-fe73-437e-8a86-996460e9b058" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="10" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceDateTaken" ma:index="11" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="13" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="d2f5926c-fefe-46c4-85d9-9ef0eea46f5c" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="MediaServiceOCR" ma:index="15" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceGenerationTime" ma:index="16" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceEventHashCode" ma:index="17" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="a2b9d960-66d6-4e1d-a64a-950bc94b8bb0" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="TaxCatchAll" ma:index="14" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{6fbb2a74-2168-4404-a595-59f9a11d4eed}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="a2b9d960-66d6-4e1d-a64a-950bc94b8bb0">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:MultiChoiceLookup">
+            <xsd:sequence>
+              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="ea7a09a4-fe73-437e-8a86-996460e9b058">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="a2b9d960-66d6-4e1d-a64a-950bc94b8bb0" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7D5976FE-8A32-4B02-AAD4-330FB68E893A}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2A73842B-19FA-47F5-8279-DD00EF3E8AFE}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7560F7E0-5B2D-4A40-BF85-2043BDA530BE}"/>
 </file>